--- a/data/trans_dic/P62A$viudedad-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P62A$viudedad-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de viudedad</t>
+          <t>Población que, al menos, percibe una pensión de viudedad (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,17</t>
+          <t>0,0; 24,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,43</t>
+          <t>0,0; 83,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,91</t>
+          <t>0,0; 52,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,3</t>
+          <t>0,0; 43,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,9</t>
+          <t>0,0; 35,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,99</t>
+          <t>0,0; 12,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 45,24</t>
+          <t>5,33; 44,96</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,03</t>
+          <t>0,0; 15,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,39; 60,37</t>
+          <t>16,17; 59,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 36,29</t>
+          <t>4,66; 36,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 19,17</t>
+          <t>2,23; 19,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 26,63</t>
+          <t>3,23; 29,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,82; 36,45</t>
+          <t>9,46; 34,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 17,66</t>
+          <t>2,11; 18,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,21</t>
+          <t>1,04; 9,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 16,38</t>
+          <t>3,04; 17,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 39,71</t>
+          <t>16,81; 41,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 11,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,07; 65,59</t>
+          <t>38,14; 65,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,96; 41,82</t>
+          <t>15,12; 42,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,82; 41,99</t>
+          <t>16,78; 43,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,76; 38,1</t>
+          <t>12,23; 38,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,51; 41,18</t>
+          <t>18,98; 39,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 22,76</t>
+          <t>7,24; 23,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 18,91</t>
+          <t>6,25; 18,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 14,41</t>
+          <t>5,01; 15,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,13; 51,76</t>
+          <t>33,34; 51,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,35; 37,28</t>
+          <t>24,02; 37,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,19; 55,05</t>
+          <t>34,51; 57,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,73; 52,12</t>
+          <t>30,54; 51,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,92; 39,32</t>
+          <t>21,69; 39,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,67; 25,29</t>
+          <t>13,46; 24,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 19,48</t>
+          <t>10,44; 18,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 19,48</t>
+          <t>10,51; 19,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 14,95</t>
+          <t>7,44; 15,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,89; 30,38</t>
+          <t>21,56; 31,26</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,89; 11,18</t>
+          <t>6,07; 10,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,74; 54,43</t>
+          <t>40,4; 54,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,99; 46,23</t>
+          <t>32,98; 46,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,02; 35,28</t>
+          <t>23,11; 35,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,2</t>
+          <t>0,61; 5,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,88; 21,7</t>
+          <t>14,96; 21,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,01; 20,75</t>
+          <t>14,03; 20,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 15,26</t>
+          <t>9,54; 15,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,16</t>
+          <t>2,2; 7,19</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,73</t>
+          <t>4,33; 8,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,22; 66,33</t>
+          <t>53,19; 66,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,15; 64,96</t>
+          <t>53,46; 65,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,04; 57,58</t>
+          <t>44,12; 57,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,65</t>
+          <t>2,77; 5,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,23; 37,0</t>
+          <t>28,48; 37,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,47; 37,01</t>
+          <t>28,23; 36,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,16; 31,32</t>
+          <t>22,82; 31,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,56</t>
+          <t>3,75; 6,4</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,98; 18,76</t>
+          <t>13,88; 18,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,97; 53,3</t>
+          <t>45,58; 53,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,81; 47,18</t>
+          <t>39,27; 46,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,94; 39,75</t>
+          <t>31,9; 39,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,94</t>
+          <t>3,18; 8,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,62; 24,17</t>
+          <t>19,55; 23,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,24; 22,3</t>
+          <t>18,26; 22,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,29; 18,06</t>
+          <t>14,41; 18,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,22; 12,97</t>
+          <t>7,07; 12,91</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de viudedad</t>
+          <t>Población que, al menos, percibe una pensión de viudedad (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 715</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1425</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1625</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1535</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 762</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1813</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1666</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1860</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1091</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1836</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1787</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2335</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1598</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4216</t>
+          <t>0; 4077</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1820</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5559</t>
+          <t>0; 6818</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5380</t>
+          <t>0; 5699</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1733</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5582</t>
+          <t>0; 5260</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6226</t>
+          <t>0; 5739</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4516</t>
+          <t>0; 5090</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1857</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1060; 9128</t>
+          <t>1076; 9072</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1988</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2076</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3847</t>
+          <t>0; 4438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3257; 11997</t>
+          <t>3213; 11826</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>237; 6998</t>
+          <t>898; 7110</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>883; 7604</t>
+          <t>886; 7861</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>928; 7629</t>
+          <t>925; 8412</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2539; 9423</t>
+          <t>2444; 9023</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>909; 7833</t>
+          <t>935; 8090</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>872; 7959</t>
+          <t>898; 7885</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1796; 9531</t>
+          <t>1766; 10276</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7407; 18155</t>
+          <t>7686; 18860</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4469</t>
+          <t>0; 5349</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2135</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2096</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20239; 35812</t>
+          <t>20824; 35941</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6142; 17170</t>
+          <t>6207; 17540</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9188; 22942</t>
+          <t>9168; 23629</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6513; 18037</t>
+          <t>5790; 18032</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7395; 16449</t>
+          <t>7583; 15976</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6926; 19766</t>
+          <t>6288; 19982</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8124; 24676</t>
+          <t>8157; 24041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6178; 18175</t>
+          <t>6325; 19911</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30379; 48932</t>
+          <t>31525; 48771</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2092</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2159</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41448; 63449</t>
+          <t>40886; 63542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26527; 43997</t>
+          <t>27579; 45558</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29421; 49910</t>
+          <t>29244; 49084</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24333; 43644</t>
+          <t>24070; 44220</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14522; 26852</t>
+          <t>14295; 26147</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26774; 48443</t>
+          <t>25960; 47046</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27968; 52446</t>
+          <t>28280; 51628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23136; 46539</t>
+          <t>23166; 47062</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>57730; 83974</t>
+          <t>59582; 86390</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4850</t>
+          <t>0; 5552</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 12121</t>
+          <t>0; 8587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17649; 33473</t>
+          <t>18181; 32915</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>70230; 96197</t>
+          <t>71405; 96096</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>74411; 104277</t>
+          <t>74394; 103895</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53876; 82569</t>
+          <t>54091; 83595</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2741; 22443</t>
+          <t>2637; 21674</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68826; 100333</t>
+          <t>69181; 101620</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74404; 110260</t>
+          <t>74539; 110631</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53276; 85025</t>
+          <t>53146; 84073</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13336; 52335</t>
+          <t>16073; 52525</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1825</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2150</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1629</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10139; 21569</t>
+          <t>10708; 22216</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>131617; 164025</t>
+          <t>131549; 163770</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>157555; 192576</t>
+          <t>158477; 192792</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>128835; 168447</t>
+          <t>129076; 168174</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8533; 18009</t>
+          <t>8846; 18361</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>128067; 167875</t>
+          <t>129216; 171514</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155218; 201812</t>
+          <t>153910; 199339</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>125756; 170030</t>
+          <t>123916; 172789</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21306; 37125</t>
+          <t>21209; 36226</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6720</t>
+          <t>0; 6964</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 12367</t>
+          <t>0; 11249</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5579</t>
+          <t>0; 5233</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>112018; 150339</t>
+          <t>111262; 149374</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>259080; 307049</t>
+          <t>262575; 309304</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>297014; 352025</t>
+          <t>292984; 349248</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>235428; 293005</t>
+          <t>235152; 292433</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>29687; 83784</t>
+          <t>29778; 83927</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257740; 317638</t>
+          <t>256818; 314441</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>294999; 360593</t>
+          <t>295256; 361475</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>234046; 295889</t>
+          <t>236126; 298549</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>125638; 225476</t>
+          <t>122995; 224531</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$viudedad-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P62A$viudedad-Edad-trans_dic.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,34</t>
+          <t>0,0; 25,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,93</t>
+          <t>0,0; 78,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,87</t>
+          <t>0,0; 53,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,64</t>
+          <t>0,0; 39,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,85</t>
+          <t>0,0; 36,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,39</t>
+          <t>0,0; 11,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 44,96</t>
+          <t>4,86; 42,46</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,03</t>
+          <t>0,0; 15,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,17; 59,51</t>
+          <t>15,63; 61,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 36,86</t>
+          <t>0,0; 32,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 19,82</t>
+          <t>2,2; 19,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 29,37</t>
+          <t>3,24; 29,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 34,9</t>
+          <t>9,45; 35,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 18,24</t>
+          <t>2,08; 17,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,13</t>
+          <t>1,01; 9,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 17,66</t>
+          <t>3,15; 17,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,81; 41,25</t>
+          <t>16,41; 40,61</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,68</t>
+          <t>0,0; 11,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,14; 65,83</t>
+          <t>35,81; 64,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,12; 42,72</t>
+          <t>14,62; 41,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,78; 43,25</t>
+          <t>16,2; 42,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,23; 38,09</t>
+          <t>12,97; 37,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,98; 39,99</t>
+          <t>17,74; 38,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 23,01</t>
+          <t>7,91; 22,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 18,43</t>
+          <t>6,91; 19,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 15,78</t>
+          <t>4,9; 15,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,34; 51,59</t>
+          <t>31,92; 49,36</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,02; 37,33</t>
+          <t>23,89; 37,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,51; 57,0</t>
+          <t>34,65; 56,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,54; 51,26</t>
+          <t>31,54; 51,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,69; 39,84</t>
+          <t>21,95; 39,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,46; 24,62</t>
+          <t>13,95; 25,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,44; 18,91</t>
+          <t>10,41; 18,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,51; 19,18</t>
+          <t>10,77; 19,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 15,12</t>
+          <t>7,47; 14,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,56; 31,26</t>
+          <t>21,19; 30,35</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,99</t>
+          <t>5,72; 10,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,4; 54,37</t>
+          <t>40,03; 54,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,98; 46,06</t>
+          <t>33,87; 46,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,11; 35,72</t>
+          <t>23,08; 34,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,03</t>
+          <t>2,73; 6,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,96; 21,98</t>
+          <t>14,62; 22,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,03; 20,82</t>
+          <t>14,29; 20,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,54; 15,09</t>
+          <t>9,29; 14,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,19</t>
+          <t>4,81; 8,1</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,99</t>
+          <t>4,1; 8,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,19; 66,22</t>
+          <t>53,49; 65,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,46; 65,04</t>
+          <t>53,82; 65,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,12; 57,49</t>
+          <t>44,13; 57,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,76</t>
+          <t>2,51; 5,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,48; 37,8</t>
+          <t>28,24; 37,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,23; 36,56</t>
+          <t>27,91; 36,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22,82; 31,82</t>
+          <t>22,96; 31,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,4</t>
+          <t>3,75; 6,38</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1702,57 +1702,57 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,88; 18,64</t>
+          <t>13,36; 18,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,58; 53,69</t>
+          <t>45,35; 53,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,27; 46,81</t>
+          <t>39,83; 47,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,9; 39,68</t>
+          <t>32,11; 39,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,95</t>
+          <t>6,87; 9,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,55; 23,93</t>
+          <t>19,41; 23,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,26; 22,35</t>
+          <t>18,14; 22,27</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,41; 18,22</t>
+          <t>14,3; 18,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,07; 12,91</t>
+          <t>10,8; 13,58</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3573</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4077</t>
+          <t>0; 4229</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6818</t>
+          <t>0; 6573</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5699</t>
+          <t>0; 5773</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5260</t>
+          <t>0; 5195</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5739</t>
+          <t>0; 5856</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5090</t>
+          <t>0; 4864</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1076; 9072</t>
+          <t>1046; 9132</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>13379</t>
         </is>
       </c>
     </row>
@@ -2494,52 +2494,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 4716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3213; 11826</t>
+          <t>3257; 12746</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>898; 7110</t>
+          <t>0; 6177</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>886; 7861</t>
+          <t>873; 7574</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>925; 8412</t>
+          <t>929; 8329</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2444; 9023</t>
+          <t>2640; 9837</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>935; 8090</t>
+          <t>923; 7884</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>898; 7885</t>
+          <t>871; 8140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1766; 10276</t>
+          <t>1831; 10044</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7686; 18860</t>
+          <t>8001; 19804</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28304</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>42515</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5349</t>
+          <t>0; 5381</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2707,47 +2707,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20824; 35941</t>
+          <t>21743; 38891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6207; 17540</t>
+          <t>6001; 17228</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9168; 23629</t>
+          <t>8849; 23201</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5790; 18032</t>
+          <t>6138; 17788</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7583; 15976</t>
+          <t>7933; 17061</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6288; 19982</t>
+          <t>6866; 19718</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8157; 24041</t>
+          <t>9014; 25513</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6325; 19911</t>
+          <t>6179; 19425</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31525; 48771</t>
+          <t>33659; 52040</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51636</t>
+          <t>52988</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20151</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71787</t>
+          <t>75597</t>
         </is>
       </c>
     </row>
@@ -2915,47 +2915,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40886; 63542</t>
+          <t>42886; 67064</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27579; 45558</t>
+          <t>27697; 45212</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29244; 49084</t>
+          <t>30200; 49511</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24070; 44220</t>
+          <t>24364; 44150</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14295; 26147</t>
+          <t>16381; 30382</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25960; 47046</t>
+          <t>25902; 46576</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28280; 51628</t>
+          <t>29000; 52790</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23166; 47062</t>
+          <t>23266; 45470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59582; 86390</t>
+          <t>62927; 90126</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34695</t>
+          <t>36319</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5552</t>
+          <t>0; 5834</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 8587</t>
+          <t>0; 10514</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3123,47 +3123,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18181; 32915</t>
+          <t>18975; 34503</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71405; 96096</t>
+          <t>70744; 96474</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>74394; 103895</t>
+          <t>76403; 104343</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54091; 83595</t>
+          <t>54026; 81727</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2637; 21674</t>
+          <t>6801; 16971</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69181; 101620</t>
+          <t>67624; 102405</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74539; 110631</t>
+          <t>75890; 109634</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53146; 84073</t>
+          <t>51799; 83368</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16073; 52525</t>
+          <t>27900; 46994</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>30157</t>
         </is>
       </c>
     </row>
@@ -3331,47 +3331,47 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10708; 22216</t>
+          <t>11133; 23439</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>131549; 163770</t>
+          <t>132281; 162840</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>158477; 192792</t>
+          <t>159549; 193382</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>129076; 168174</t>
+          <t>129110; 168770</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8846; 18361</t>
+          <t>8755; 18756</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>129216; 171514</t>
+          <t>128128; 169366</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>153910; 199339</t>
+          <t>152181; 199970</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>123916; 172789</t>
+          <t>124663; 170445</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21209; 36226</t>
+          <t>23285; 39562</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>135375</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>190581</t>
+          <t>201539</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6964</t>
+          <t>0; 6903</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 11249</t>
+          <t>0; 11048</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5233</t>
+          <t>0; 5593</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>111262; 149374</t>
+          <t>116805; 157654</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>262575; 309304</t>
+          <t>261261; 309755</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>292984; 349248</t>
+          <t>297201; 351962</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>235152; 292433</t>
+          <t>236685; 291509</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>29778; 83927</t>
+          <t>55192; 78578</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>256818; 314441</t>
+          <t>255092; 312903</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>295256; 361475</t>
+          <t>293362; 360159</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>236126; 298549</t>
+          <t>234246; 297540</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>122995; 224531</t>
+          <t>181275; 227978</t>
         </is>
       </c>
     </row>
